--- a/MY CLASSES/RE-ASSESSMENTS/COTATION SHEET_L 4 NETWORKING AND INTERNET TECHNOLOGY-IOT-WEB-APP.xlsx
+++ b/MY CLASSES/RE-ASSESSMENTS/COTATION SHEET_L 4 NETWORKING AND INTERNET TECHNOLOGY-IOT-WEB-APP.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Landry\3D Objects\ETEFOP Trainer Docs\Revised_COTATION SHEETS THIRD TERM 2024-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Landry\3D Objects\ETEFOP Trainer Docs\ETEFOP-DOCS\MY CLASSES\RE-ASSESSMENTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="129">
   <si>
     <t>ACADEMIC YEAR 2024-2025</t>
   </si>
@@ -405,6 +405,15 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>NTWARI KUNDA Aldo Serge</t>
+  </si>
+  <si>
+    <t>MUHIRE Germain</t>
+  </si>
+  <si>
+    <t>ISUBIRIZIGIHE Inglid Schiphra</t>
   </si>
 </sst>
 </file>
@@ -775,7 +784,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
@@ -923,6 +932,34 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2226,16 +2263,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="14"/>
-      <c r="D10" s="55" t="s">
+      <c r="D10" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
@@ -2244,10 +2281,10 @@
     </row>
     <row r="11" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="56"/>
+      <c r="C11" s="63"/>
       <c r="D11" s="16" t="s">
         <v>4</v>
       </c>
@@ -2279,23 +2316,23 @@
     </row>
     <row r="13" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="59" t="s">
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
+      <c r="N13" s="67"/>
       <c r="O13" s="17"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
@@ -2305,25 +2342,25 @@
     </row>
     <row r="14" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="64" t="s">
+      <c r="C14" s="69"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="65" t="s">
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
-      <c r="N14" s="65"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
       <c r="O14" s="18" t="s">
         <v>10</v>
       </c>
@@ -2335,25 +2372,25 @@
     </row>
     <row r="15" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="41" t="s">
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="41" t="s">
+      <c r="F15" s="49"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="43"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="50"/>
       <c r="O15" s="19"/>
       <c r="P15" s="9" t="str">
         <f>IF(O15="SM","0.7",IF(O15="GM","0.5",IF(O15="CM","0.5","")))</f>
@@ -2366,31 +2403,31 @@
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="49" t="s">
+      <c r="E16" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="51"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="58"/>
       <c r="K16" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="L16" s="52" t="s">
+      <c r="L16" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="M16" s="53"/>
-      <c r="N16" s="54"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="61"/>
       <c r="O16" s="21"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
@@ -2400,9 +2437,9 @@
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="48"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="55"/>
       <c r="E17" s="22" t="s">
         <v>20</v>
       </c>
@@ -2445,9 +2482,9 @@
     </row>
     <row r="18" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="55"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
       <c r="G18" s="25"/>
@@ -2459,7 +2496,9 @@
       <c r="K18" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="L18" s="25"/>
+      <c r="L18" s="25">
+        <v>15</v>
+      </c>
       <c r="M18" s="25"/>
       <c r="N18" s="25"/>
       <c r="O18" s="27" t="s">
@@ -2492,14 +2531,14 @@
         <v/>
       </c>
       <c r="K19" s="33" t="str">
-        <f t="shared" ref="K19:K65" si="1">IF($O$15="","",IF(ISTEXT(J19),"",IF(J19&gt;=$K$17*$P$15,"Competent","Not yet Competent")))</f>
+        <f t="shared" ref="K19:K64" si="1">IF($O$15="","",IF(ISTEXT(J19),"",IF(J19&gt;=$K$17*$P$15,"Competent","Not yet Competent")))</f>
         <v/>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="34"/>
       <c r="N19" s="34"/>
       <c r="O19" s="33" t="str">
-        <f t="shared" ref="O19:O65" si="2">IFERROR(IF(AND(ISNUMBER(J19),J19&gt;=$K$17*$P$15)," ",IF(AND(J19&gt;0,$O$16&lt;&gt;"Not yet Taught",$D19&lt;&gt;"",J19="-"),"Not yet Assessed",IF(AND($O$16="Completed",$D19&lt;&gt;"",$L$18&gt;0,L19&gt;0,L19&gt;=$L$18*$P$15),"Competent",IF(AND($O$16="Completed",$M$18&gt;0,$D19&lt;&gt;"",M19&gt;0,M19&gt;=$M$18*$P$15),"Competent",IF(AND($O$16="Completed",$N$18&gt;0,$D19&lt;&gt;"",N19&gt;0,N19&gt;=$N$18*$P$15),"Competent",IF(AND($O$16="Completed",$D19&lt;&gt;"",L19&lt;$N$18*$P$15),"Re-Assessment",IF(AND($O$16="Completed",SUM($N$18:$N$18)&lt;=0,$D19&lt;&gt;"",L19&lt;=0,M19&lt;=0,N19&lt;=0),"Re-Assessment",IF(AND(J19&gt;0,$D19&lt;&gt;"",$O$16="Ongoing"),"Ongoing","")))))))),"")</f>
+        <f t="shared" ref="O19:O64" si="2">IFERROR(IF(AND(ISNUMBER(J19),J19&gt;=$K$17*$P$15)," ",IF(AND(J19&gt;0,$O$16&lt;&gt;"Not yet Taught",$D19&lt;&gt;"",J19="-"),"Not yet Assessed",IF(AND($O$16="Completed",$D19&lt;&gt;"",$L$18&gt;0,L19&gt;0,L19&gt;=$L$18*$P$15),"Competent",IF(AND($O$16="Completed",$M$18&gt;0,$D19&lt;&gt;"",M19&gt;0,M19&gt;=$M$18*$P$15),"Competent",IF(AND($O$16="Completed",$N$18&gt;0,$D19&lt;&gt;"",N19&gt;0,N19&gt;=$N$18*$P$15),"Competent",IF(AND($O$16="Completed",$D19&lt;&gt;"",L19&lt;$N$18*$P$15),"Re-Assessment",IF(AND($O$16="Completed",SUM($N$18:$N$18)&lt;=0,$D19&lt;&gt;"",L19&lt;=0,M19&lt;=0,N19&lt;=0),"Re-Assessment",IF(AND(J19&gt;0,$D19&lt;&gt;"",$O$16="Ongoing"),"Ongoing","")))))))),"")</f>
         <v/>
       </c>
       <c r="P19" s="9"/>
@@ -2681,7 +2720,7 @@
         <v/>
       </c>
       <c r="L24" s="34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="M24" s="34"/>
       <c r="N24" s="34"/>
@@ -2794,7 +2833,7 @@
         <v/>
       </c>
       <c r="L27" s="34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="M27" s="34"/>
       <c r="N27" s="34"/>
@@ -4202,7 +4241,7 @@
         <v/>
       </c>
       <c r="K65" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($O$15="","",IF(ISTEXT(J65),"",IF(J65&gt;=$K$17*$P$15,"Competent","Not yet Competent")))</f>
         <v/>
       </c>
       <c r="L65" s="34">
@@ -4211,7 +4250,7 @@
       <c r="M65" s="34"/>
       <c r="N65" s="34"/>
       <c r="O65" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f>IFERROR(IF(AND(ISNUMBER(J65),J65&gt;=$K$17*$P$15)," ",IF(AND(J65&gt;0,$O$16&lt;&gt;"Not yet Taught",$D65&lt;&gt;"",J65="-"),"Not yet Assessed",IF(AND($O$16="Completed",$D65&lt;&gt;"",$L$18&gt;0,L65&gt;0,L65&gt;=$L$18*$P$15),"Competent",IF(AND($O$16="Completed",$M$18&gt;0,$D65&lt;&gt;"",M65&gt;0,M65&gt;=$M$18*$P$15),"Competent",IF(AND($O$16="Completed",$N$18&gt;0,$D65&lt;&gt;"",N65&gt;0,N65&gt;=$N$18*$P$15),"Competent",IF(AND($O$16="Completed",$D65&lt;&gt;"",L65&lt;$N$18*$P$15),"Re-Assessment",IF(AND($O$16="Completed",SUM($N$18:$N$18)&lt;=0,$D65&lt;&gt;"",L65&lt;=0,M65&lt;=0,N65&lt;=0),"Re-Assessment",IF(AND(J65&gt;0,$D65&lt;&gt;"",$O$16="Ongoing"),"Ongoing","")))))))),"")</f>
         <v/>
       </c>
       <c r="P65" s="9"/>
@@ -4222,20 +4261,26 @@
     </row>
     <row r="66" spans="1:36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="9"/>
-      <c r="B66" s="36"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="37"/>
-      <c r="H66" s="37"/>
-      <c r="I66" s="37"/>
-      <c r="J66" s="32"/>
-      <c r="K66" s="33"/>
-      <c r="L66" s="34"/>
-      <c r="M66" s="34"/>
-      <c r="N66" s="34"/>
-      <c r="O66" s="33"/>
+      <c r="B66" s="40">
+        <v>48</v>
+      </c>
+      <c r="C66" s="41"/>
+      <c r="D66" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="43"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="41"/>
+      <c r="L66" s="45">
+        <v>14</v>
+      </c>
+      <c r="M66" s="45"/>
+      <c r="N66" s="45"/>
+      <c r="O66" s="41"/>
       <c r="P66" s="9"/>
       <c r="Q66" s="9"/>
       <c r="R66" s="9"/>
@@ -4265,20 +4310,26 @@
     </row>
     <row r="67" spans="1:36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9"/>
-      <c r="B67" s="28"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="35"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="37"/>
-      <c r="H67" s="37"/>
-      <c r="I67" s="37"/>
-      <c r="J67" s="32"/>
-      <c r="K67" s="33"/>
-      <c r="L67" s="34"/>
-      <c r="M67" s="34"/>
-      <c r="N67" s="34"/>
-      <c r="O67" s="33"/>
+      <c r="B67" s="46">
+        <v>49</v>
+      </c>
+      <c r="C67" s="41"/>
+      <c r="D67" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="43"/>
+      <c r="J67" s="44"/>
+      <c r="K67" s="41"/>
+      <c r="L67" s="45">
+        <v>7</v>
+      </c>
+      <c r="M67" s="45"/>
+      <c r="N67" s="45"/>
+      <c r="O67" s="41"/>
       <c r="P67" s="9"/>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -4311,20 +4362,26 @@
     </row>
     <row r="68" spans="1:36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9"/>
-      <c r="B68" s="36"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="37"/>
-      <c r="I68" s="37"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="33"/>
-      <c r="L68" s="34"/>
-      <c r="M68" s="34"/>
-      <c r="N68" s="34"/>
-      <c r="O68" s="33"/>
+      <c r="B68" s="40">
+        <v>50</v>
+      </c>
+      <c r="C68" s="41"/>
+      <c r="D68" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="E68" s="43"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43"/>
+      <c r="H68" s="43"/>
+      <c r="I68" s="43"/>
+      <c r="J68" s="44"/>
+      <c r="K68" s="41"/>
+      <c r="L68" s="45">
+        <v>9</v>
+      </c>
+      <c r="M68" s="45"/>
+      <c r="N68" s="45"/>
+      <c r="O68" s="41"/>
       <c r="P68" s="9"/>
       <c r="Q68" s="9"/>
       <c r="R68" s="9"/>
